--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Lab Observation: Microbiology, ResourceType Observation, Variation Bacteriology</t>
+    <t>This StructureDefinition contains the maps for VistA MICROBIOLOGY (file 63.05) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="458">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -459,7 +459,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
+    <t>http://va.gov/fhir/ValueSet/VFLabObservationStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -875,6 +875,9 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VFPositiveNegative</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1443,6 +1446,9 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VFAntibioticSensitivityInterpretation</t>
   </si>
   <si>
     <t>1524: terminologyMaps using VF_AntibioticSensitivityInterpretation on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5.1 to 160.1)</t>
@@ -1797,7 +1803,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.1640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="14.109375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5173,13 +5179,11 @@
         <v>40</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>40</v>
+        <v>271</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>40</v>
@@ -5197,7 +5201,7 @@
         <v>40</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
@@ -5218,10 +5222,10 @@
         <v>40</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>40</v>
@@ -5230,18 +5234,18 @@
         <v>40</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5267,16 +5271,16 @@
         <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>40</v>
@@ -5325,7 +5329,7 @@
         <v>40</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -5346,10 +5350,10 @@
         <v>40</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>40</v>
@@ -5366,13 +5370,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>236</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>40</v>
@@ -5488,18 +5492,18 @@
         <v>248</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5525,16 +5529,16 @@
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>40</v>
@@ -5563,7 +5567,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>40</v>
@@ -5581,7 +5585,7 @@
         <v>40</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -5590,7 +5594,7 @@
         <v>50</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>62</v>
@@ -5605,7 +5609,7 @@
         <v>93</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>40</v>
@@ -5622,14 +5626,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5651,16 +5655,16 @@
         <v>149</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>40</v>
@@ -5688,10 +5692,10 @@
         <v>169</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>40</v>
@@ -5709,7 +5713,7 @@
         <v>40</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
@@ -5727,19 +5731,19 @@
         <v>40</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>40</v>
@@ -5750,10 +5754,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5776,19 +5780,19 @@
         <v>40</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>40</v>
@@ -5837,7 +5841,7 @@
         <v>40</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -5858,10 +5862,10 @@
         <v>40</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>40</v>
@@ -5878,10 +5882,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5907,13 +5911,13 @@
         <v>149</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5939,13 +5943,13 @@
         <v>40</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>40</v>
@@ -5963,7 +5967,7 @@
         <v>40</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -5981,19 +5985,19 @@
         <v>40</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>40</v>
@@ -6004,10 +6008,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6033,16 +6037,16 @@
         <v>149</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>40</v>
@@ -6067,13 +6071,13 @@
         <v>40</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>40</v>
@@ -6091,7 +6095,7 @@
         <v>40</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
@@ -6112,10 +6116,10 @@
         <v>40</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>40</v>
@@ -6132,10 +6136,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6158,16 +6162,16 @@
         <v>40</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6217,7 +6221,7 @@
         <v>40</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>38</v>
@@ -6235,19 +6239,19 @@
         <v>40</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>40</v>
@@ -6258,10 +6262,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6284,16 +6288,16 @@
         <v>40</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6343,7 +6347,7 @@
         <v>40</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -6361,19 +6365,19 @@
         <v>40</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>40</v>
@@ -6384,10 +6388,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6410,19 +6414,19 @@
         <v>40</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>40</v>
@@ -6471,7 +6475,7 @@
         <v>40</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -6483,7 +6487,7 @@
         <v>40</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>40</v>
@@ -6492,10 +6496,10 @@
         <v>40</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>40</v>
@@ -6512,10 +6516,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6636,10 +6640,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6762,14 +6766,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6791,10 +6795,10 @@
         <v>96</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>99</v>
@@ -6849,7 +6853,7 @@
         <v>40</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>38</v>
@@ -6890,10 +6894,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6916,13 +6920,13 @@
         <v>40</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6973,7 +6977,7 @@
         <v>40</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>38</v>
@@ -6982,7 +6986,7 @@
         <v>50</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>62</v>
@@ -6994,10 +6998,10 @@
         <v>40</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>40</v>
@@ -7014,10 +7018,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7040,13 +7044,13 @@
         <v>40</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7097,7 +7101,7 @@
         <v>40</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>38</v>
@@ -7106,7 +7110,7 @@
         <v>50</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>62</v>
@@ -7118,10 +7122,10 @@
         <v>40</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>40</v>
@@ -7138,10 +7142,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7167,16 +7171,16 @@
         <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>40</v>
@@ -7204,10 +7208,10 @@
         <v>74</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>40</v>
@@ -7225,7 +7229,7 @@
         <v>40</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>38</v>
@@ -7243,13 +7247,13 @@
         <v>40</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>40</v>
@@ -7266,10 +7270,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7295,16 +7299,16 @@
         <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>40</v>
@@ -7329,13 +7333,13 @@
         <v>40</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>40</v>
@@ -7353,7 +7357,7 @@
         <v>40</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -7371,13 +7375,13 @@
         <v>40</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>40</v>
@@ -7394,10 +7398,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7420,17 +7424,17 @@
         <v>40</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>40</v>
@@ -7479,7 +7483,7 @@
         <v>40</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -7503,7 +7507,7 @@
         <v>40</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>40</v>
@@ -7520,10 +7524,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7549,10 +7553,10 @@
         <v>253</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7603,7 +7607,7 @@
         <v>40</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
@@ -7624,10 +7628,10 @@
         <v>40</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>40</v>
@@ -7644,10 +7648,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7670,16 +7674,16 @@
         <v>51</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7729,7 +7733,7 @@
         <v>40</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
@@ -7750,10 +7754,10 @@
         <v>40</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>40</v>
@@ -7770,10 +7774,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7796,16 +7800,16 @@
         <v>51</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7855,7 +7859,7 @@
         <v>40</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>38</v>
@@ -7876,10 +7880,10 @@
         <v>40</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>40</v>
@@ -7896,10 +7900,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7922,19 +7926,19 @@
         <v>51</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>40</v>
@@ -7983,7 +7987,7 @@
         <v>40</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
@@ -8004,10 +8008,10 @@
         <v>40</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>40</v>
@@ -8024,10 +8028,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8148,10 +8152,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8274,14 +8278,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8303,10 +8307,10 @@
         <v>96</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>99</v>
@@ -8361,7 +8365,7 @@
         <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
@@ -8402,10 +8406,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8431,13 +8435,13 @@
         <v>149</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>168</v>
@@ -8465,10 +8469,10 @@
         <v>40</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>171</v>
@@ -8489,7 +8493,7 @@
         <v>40</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>50</v>
@@ -8507,7 +8511,7 @@
         <v>40</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>174</v>
@@ -8525,15 +8529,15 @@
         <v>40</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8559,13 +8563,13 @@
         <v>237</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>241</v>
@@ -8615,7 +8619,7 @@
         <v>157</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
@@ -8633,7 +8637,7 @@
         <v>40</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>246</v>
@@ -8656,13 +8660,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>40</v>
@@ -8687,13 +8691,13 @@
         <v>253</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>241</v>
@@ -8745,7 +8749,7 @@
         <v>40</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
@@ -8763,7 +8767,7 @@
         <v>40</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>246</v>
@@ -8781,15 +8785,15 @@
         <v>40</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8815,16 +8819,16 @@
         <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>40</v>
@@ -8852,10 +8856,10 @@
         <v>169</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>40</v>
@@ -8873,7 +8877,7 @@
         <v>40</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
@@ -8882,7 +8886,7 @@
         <v>50</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>62</v>
@@ -8897,7 +8901,7 @@
         <v>93</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>40</v>
@@ -8914,14 +8918,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8943,16 +8947,16 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>40</v>
@@ -8977,13 +8981,11 @@
         <v>40</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>304</v>
+        <v>453</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>40</v>
@@ -9001,7 +9003,7 @@
         <v>40</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
@@ -9019,33 +9021,33 @@
         <v>40</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9071,16 +9073,16 @@
         <v>41</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>40</v>
@@ -9129,7 +9131,7 @@
         <v>40</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>38</v>
@@ -9150,10 +9152,10 @@
         <v>40</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>40</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -609,10 +609,10 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
+  </si>
+  <si>
     <t>Micro.Microbiology.BacteriologyReportStatus</t>
-  </si>
-  <si>
-    <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -1021,12 +1021,12 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>1516: terminologyMaps using VF_PositiveNegative on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
+  </si>
+  <si>
     <t>Micro.Microbiology.UrineScreen</t>
   </si>
   <si>
-    <t>1516: terminologyMaps using VF_PositiveNegative on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
-  </si>
-  <si>
     <t>Observation.value[x]:valueCodeableConcept.text</t>
   </si>
   <si>
@@ -1060,10 +1060,10 @@
     <t>valueString</t>
   </si>
   <si>
+    <t>1518: source value from MICROBIOLOGY - GRAM STAIN &gt; GRAM STAIN - GRAM STAIN (#63.05-11.6 &gt; 63.29-.01)</t>
+  </si>
+  <si>
     <t>Micro.BacteriologyReports.GramStain</t>
-  </si>
-  <si>
-    <t>1518: source value from MICROBIOLOGY - GRAM STAIN &gt; GRAM STAIN - GRAM STAIN (#63.05-11.6 &gt; 63.29-.01)</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1953,8 +1953,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="222.515625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="222.515625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4107,10 +4107,10 @@
         <v>221</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>222</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -8793,10 +8793,10 @@
         <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -9049,10 +9049,10 @@
         <v>292</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9303,10 +9303,10 @@
         <v>353</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>84</v>
+        <v>498</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>498</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -693,6 +693,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-10:1525: fixed value without value? if MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL {null}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -4086,28 +4090,28 @@
         <v>84</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4115,10 +4119,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4141,19 +4145,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4202,7 +4206,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4217,19 +4221,19 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>84</v>
@@ -4243,10 +4247,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4269,16 +4273,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4328,7 +4332,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4349,13 +4353,13 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>84</v>
@@ -4369,14 +4373,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4395,19 +4399,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4456,7 +4460,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4471,19 +4475,19 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>84</v>
@@ -4497,14 +4501,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4523,19 +4527,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4584,7 +4588,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4593,25 +4597,25 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>84</v>
@@ -4625,10 +4629,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4651,16 +4655,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4710,7 +4714,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4731,13 +4735,13 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>84</v>
@@ -4751,10 +4755,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4777,17 +4781,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4836,7 +4840,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4851,19 +4855,19 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
@@ -4877,10 +4881,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4903,19 +4907,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4952,7 +4956,7 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
@@ -4962,7 +4966,7 @@
         <v>201</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4971,28 +4975,28 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5003,13 +5007,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>84</v>
@@ -5034,16 +5038,16 @@
         <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5092,7 +5096,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5101,28 +5105,28 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5133,10 +5137,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5159,13 +5163,13 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5216,7 +5220,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5240,7 +5244,7 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5257,10 +5261,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5289,7 +5293,7 @@
         <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>143</v>
@@ -5330,10 +5334,10 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
@@ -5342,7 +5346,7 @@
         <v>201</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5366,7 +5370,7 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>84</v>
@@ -5383,10 +5387,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5409,19 +5413,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5450,7 +5454,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5468,7 +5472,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5489,10 +5493,10 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>84</v>
@@ -5501,18 +5505,18 @@
         <v>84</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5535,19 +5539,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5596,7 +5600,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5617,10 +5621,10 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
@@ -5637,13 +5641,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>84</v>
@@ -5665,19 +5669,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5726,7 +5730,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5735,42 +5739,42 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5796,16 +5800,16 @@
         <v>193</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5834,7 +5838,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -5852,7 +5856,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5861,7 +5865,7 @@
         <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>106</v>
@@ -5876,7 +5880,7 @@
         <v>137</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -5893,14 +5897,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5922,16 +5926,16 @@
         <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5959,10 +5963,10 @@
         <v>213</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>84</v>
@@ -5980,7 +5984,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5998,19 +6002,19 @@
         <v>84</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6021,10 +6025,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6047,19 +6051,19 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6108,7 +6112,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6129,10 +6133,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6149,10 +6153,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6178,13 +6182,13 @@
         <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6210,13 +6214,13 @@
         <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -6234,7 +6238,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6252,19 +6256,19 @@
         <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6275,10 +6279,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6304,16 +6308,16 @@
         <v>193</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6338,13 +6342,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6362,7 +6366,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6383,10 +6387,10 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
@@ -6403,10 +6407,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6429,16 +6433,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6488,7 +6492,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6506,19 +6510,19 @@
         <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6529,10 +6533,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6555,16 +6559,16 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6614,7 +6618,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6632,19 +6636,19 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6655,10 +6659,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6681,19 +6685,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6742,7 +6746,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6754,7 +6758,7 @@
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -6763,10 +6767,10 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6783,10 +6787,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6809,13 +6813,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6866,7 +6870,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6890,7 +6894,7 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
@@ -6907,10 +6911,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6939,7 +6943,7 @@
         <v>141</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>143</v>
@@ -6992,7 +6996,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7016,7 +7020,7 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7033,14 +7037,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7062,10 +7066,10 @@
         <v>140</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>143</v>
@@ -7120,7 +7124,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7161,10 +7165,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7187,13 +7191,13 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7244,7 +7248,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7253,7 +7257,7 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
@@ -7265,10 +7269,10 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
@@ -7285,10 +7289,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7311,13 +7315,13 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7368,7 +7372,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7377,7 +7381,7 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
@@ -7389,10 +7393,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7409,10 +7413,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7438,16 +7442,16 @@
         <v>193</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7475,10 +7479,10 @@
         <v>118</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7496,7 +7500,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7514,13 +7518,13 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7537,10 +7541,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7566,16 +7570,16 @@
         <v>193</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7600,13 +7604,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7624,7 +7628,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7642,13 +7646,13 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -7665,10 +7669,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7691,17 +7695,17 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7750,7 +7754,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7774,7 +7778,7 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -7791,10 +7795,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7817,13 +7821,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7874,7 +7878,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7895,10 +7899,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -7915,10 +7919,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7941,16 +7945,16 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8000,7 +8004,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8021,10 +8025,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8041,10 +8045,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8067,16 +8071,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8126,7 +8130,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8147,10 +8151,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8167,10 +8171,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8193,19 +8197,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8254,7 +8258,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8275,10 +8279,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8295,10 +8299,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8321,13 +8325,13 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8378,7 +8382,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8402,7 +8406,7 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8419,10 +8423,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8451,7 +8455,7 @@
         <v>141</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>143</v>
@@ -8504,7 +8508,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8528,7 +8532,7 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8545,14 +8549,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8574,10 +8578,10 @@
         <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>143</v>
@@ -8632,7 +8636,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8673,10 +8677,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8702,13 +8706,13 @@
         <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>212</v>
@@ -8736,10 +8740,10 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>215</v>
@@ -8760,7 +8764,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>94</v>
@@ -8778,22 +8782,22 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -8801,10 +8805,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8827,19 +8831,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8876,7 +8880,7 @@
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -8886,7 +8890,7 @@
         <v>201</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8904,19 +8908,19 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -8927,13 +8931,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -8955,19 +8959,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9016,7 +9020,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9034,22 +9038,22 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -9057,10 +9061,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9086,16 +9090,16 @@
         <v>193</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9123,10 +9127,10 @@
         <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9144,7 +9148,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9153,7 +9157,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9168,7 +9172,7 @@
         <v>137</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9185,14 +9189,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9214,16 +9218,16 @@
         <v>193</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9252,25 +9256,25 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9288,22 +9292,22 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -9311,10 +9315,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9340,16 +9344,16 @@
         <v>85</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9398,7 +9402,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9419,10 +9423,10 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -696,7 +696,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-10:1525: fixed value without value? if MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL {null}</t>
+inv-11:1525: fixed value without value? if MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL {null}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1537,7 +1537,7 @@
 &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5 to 160)</t>
+    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5+to+160)</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -1558,7 +1558,7 @@
     <t>Observation.component.value[x]:valueString</t>
   </si>
   <si>
-    <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5 to 160)</t>
+    <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5+to+160)</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservationBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA MICROBIOLOGY (file 63.05) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -696,7 +696,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-11:1525: fixed value without value? if MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL {null}</t>
+inv-11:1525: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL {null}</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -717,7 +717,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1525: fixed value without value? if MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL</t>
+    <t>1525: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1957,7 +1957,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="222.515625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="226.3125" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
